--- a/src/assets/modelo-importacao-alunos.xlsx
+++ b/src/assets/modelo-importacao-alunos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PI-5\Braille-Frontend\Braille-Frontend\dist\Braille-Frontend\browser\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sande\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{713ABD51-8C7C-4718-BA6C-C57D4BF08C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C63365F-B4C8-4BA4-93DF-833D1FF766C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,19 +17,16 @@
     <sheet name="Instruções" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dados!$A$2:$X$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dados!$A$2:$Y$2</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="71">
   <si>
     <t>NomeCompleto</t>
-  </si>
-  <si>
-    <t>CPF_RG</t>
   </si>
   <si>
     <t>DataNascimento</t>
@@ -195,11 +192,6 @@
 EX: SP, RJ, MG, etc.</t>
   </si>
   <si>
-    <t>Ex: 123.456.789-00 
-ou 
-RG equivalente</t>
-  </si>
-  <si>
     <t>DataNascimento
 DD/MM/AAAA (ex: 15/03/1985)</t>
   </si>
@@ -237,6 +229,18 @@
   </si>
   <si>
     <t>Como você se considera em relação à sua cor ou raça?</t>
+  </si>
+  <si>
+    <t>RG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ex: 123.456.789-00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ou </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ex: 11.111.111 </t>
   </si>
 </sst>
 </file>
@@ -736,49 +740,51 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:Y2"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.875" customWidth="1"/>
-    <col min="2" max="2" width="17.625" customWidth="1"/>
-    <col min="3" max="12" width="22.875" customWidth="1"/>
-    <col min="13" max="13" width="14.75" customWidth="1"/>
-    <col min="14" max="14" width="24.125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="24.125" customWidth="1"/>
-    <col min="16" max="24" width="22.875" customWidth="1"/>
+    <col min="1" max="2" width="22.875" customWidth="1"/>
+    <col min="3" max="3" width="17.625" customWidth="1"/>
+    <col min="4" max="13" width="22.875" customWidth="1"/>
+    <col min="14" max="14" width="14.75" customWidth="1"/>
+    <col min="15" max="15" width="24.125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="24.125" customWidth="1"/>
+    <col min="17" max="25" width="22.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="4" customFormat="1" ht="53.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" s="4" customFormat="1" ht="53.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D1" s="7"/>
+        <v>70</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="E1" s="7"/>
       <c r="F1" s="7"/>
-      <c r="G1" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="H1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="6" t="s">
+        <v>56</v>
+      </c>
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
       <c r="K1" s="7"/>
       <c r="L1" s="7"/>
-      <c r="M1" s="6" t="s">
-        <v>55</v>
-      </c>
+      <c r="M1" s="7"/>
       <c r="N1" s="6" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="P1" s="7"/>
+        <v>57</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>66</v>
+      </c>
       <c r="Q1" s="7"/>
       <c r="R1" s="7"/>
       <c r="S1" s="7"/>
@@ -786,144 +792,136 @@
       <c r="U1" s="7"/>
       <c r="V1" s="7"/>
       <c r="W1" s="7"/>
-      <c r="X1" s="8"/>
-    </row>
-    <row r="2" spans="1:24" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="X1" s="7"/>
+      <c r="Y1" s="8"/>
+    </row>
+    <row r="2" spans="1:25" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="E2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="F2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="G2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="H2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="I2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="J2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="K2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="L2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="M2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="N2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="O2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="10" t="s">
+      <c r="P2" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="P2" s="10" t="s">
+      <c r="R2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="10" t="s">
+      <c r="S2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="R2" s="10" t="s">
+      <c r="T2" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="S2" s="10" t="s">
+      <c r="U2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="T2" s="10" t="s">
+      <c r="V2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="U2" s="10" t="s">
+      <c r="W2" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="V2" s="10" t="s">
+      <c r="X2" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="W2" s="10" t="s">
+      <c r="Y2" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="X2" s="11" t="s">
-        <v>22</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:X2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:Y2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
-    <ignoredError sqref="P2:X2 A2:N2" numberStoredAsText="1"/>
+    <ignoredError sqref="Q2:Y2 D2:O2 A2" numberStoredAsText="1"/>
   </ignoredErrors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="9">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4467A07B-7F0C-4637-868F-E10C8EC785C4}">
-          <x14:formula1>
-            <xm:f>Instruções!$A$3:$A$6</xm:f>
-          </x14:formula1>
-          <xm:sqref>D3:D6457</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{34221C54-0930-4859-928F-1EF5AA43CF5F}">
-          <x14:formula1>
-            <xm:f>Instruções!$C$3:$C$7</xm:f>
-          </x14:formula1>
-          <xm:sqref>E3:E6457</xm:sqref>
-        </x14:dataValidation>
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{19035003-A070-4FF7-BD0C-8418E5EC12A0}">
           <x14:formula1>
             <xm:f>Instruções!$E$3:$E$5</xm:f>
           </x14:formula1>
-          <xm:sqref>P3:P6457</xm:sqref>
+          <xm:sqref>I3:I6457</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B3928D14-F069-43F0-B787-22BED2FA21D5}">
           <x14:formula1>
             <xm:f>Instruções!$A$10:$A$11</xm:f>
           </x14:formula1>
-          <xm:sqref>Q3:Q6457</xm:sqref>
+          <xm:sqref>J3:J6457</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C0860636-1AC8-4C3F-914C-34578DF95BBA}">
           <x14:formula1>
             <xm:f>Instruções!$E$10:$E$17</xm:f>
           </x14:formula1>
-          <xm:sqref>R3:R6457</xm:sqref>
+          <xm:sqref>K3:K6457</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F13234A7-3F0D-4F57-A847-CE63B53E5D99}">
           <x14:formula1>
             <xm:f>Instruções!$G$3:$G$5</xm:f>
           </x14:formula1>
-          <xm:sqref>T3:T6457</xm:sqref>
+          <xm:sqref>M3:M6457</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{11DDE071-7C92-4D37-9379-4ADFD1483A76}">
           <x14:formula1>
             <xm:f>Instruções!$C$10:$C$11</xm:f>
           </x14:formula1>
-          <xm:sqref>W3:W6457</xm:sqref>
+          <xm:sqref>P3:P6457</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E5A8A6B5-9503-40D9-8734-778FC837BB6A}">
           <x14:formula1>
             <xm:f>Instruções!$I$3:$I$6</xm:f>
           </x14:formula1>
-          <xm:sqref>X3:X6457</xm:sqref>
+          <xm:sqref>Q3:Q6457</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BD25C12D-0A9B-467C-A431-536F15A75328}">
           <x14:formula1>
             <xm:f>Instruções!$G$10:$G$15</xm:f>
           </x14:formula1>
-          <xm:sqref>O3:O3595</xm:sqref>
+          <xm:sqref>H3:H3595</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -950,171 +948,171 @@
     <row r="1" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C7" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="G9" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="G10" s="12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E12" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E13" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E14" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E15" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E16" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="5:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E17" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/src/assets/modelo-importacao-alunos.xlsx
+++ b/src/assets/modelo-importacao-alunos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sande\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PI-5\Braille-Frontend\src\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C63365F-B4C8-4BA4-93DF-833D1FF766C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DACF511-22B7-440C-B304-116CEDFD17D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -237,10 +237,10 @@
     <t xml:space="preserve">Ex: 123.456.789-00 </t>
   </si>
   <si>
-    <t xml:space="preserve">ou </t>
-  </si>
-  <si>
     <t xml:space="preserve">Ex: 11.111.111 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPF </t>
   </si>
 </sst>
 </file>
@@ -760,7 +760,7 @@
         <v>68</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>55</v>
@@ -800,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>67</v>

--- a/src/assets/modelo-importacao-alunos.xlsx
+++ b/src/assets/modelo-importacao-alunos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PI-5\Braille-Frontend\src\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DACF511-22B7-440C-B304-116CEDFD17D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33D41E79-CACD-4A01-97E4-3AB02988D79B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -240,7 +240,7 @@
     <t xml:space="preserve">Ex: 11.111.111 </t>
   </si>
   <si>
-    <t xml:space="preserve">CPF </t>
+    <t>CPF</t>
   </si>
 </sst>
 </file>
@@ -873,55 +873,60 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Y2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
-    <ignoredError sqref="Q2:Y2 D2:O2 A2" numberStoredAsText="1"/>
+    <ignoredError sqref="T2:W2 N2:O2 L2" numberStoredAsText="1"/>
   </ignoredErrors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="8">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{19035003-A070-4FF7-BD0C-8418E5EC12A0}">
           <x14:formula1>
             <xm:f>Instruções!$E$3:$E$5</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I6457</xm:sqref>
+          <xm:sqref>Q3:Q1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B3928D14-F069-43F0-B787-22BED2FA21D5}">
           <x14:formula1>
             <xm:f>Instruções!$A$10:$A$11</xm:f>
           </x14:formula1>
-          <xm:sqref>J3:J6457</xm:sqref>
+          <xm:sqref>R3:R1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C0860636-1AC8-4C3F-914C-34578DF95BBA}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E5A8A6B5-9503-40D9-8734-778FC837BB6A}">
           <x14:formula1>
-            <xm:f>Instruções!$E$10:$E$17</xm:f>
+            <xm:f>Instruções!$I$3:$I$6</xm:f>
           </x14:formula1>
-          <xm:sqref>K3:K6457</xm:sqref>
+          <xm:sqref>Y3:Y1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F13234A7-3F0D-4F57-A847-CE63B53E5D99}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C90C44D7-77A9-49A0-8B19-39D588AC2DD8}">
           <x14:formula1>
-            <xm:f>Instruções!$G$3:$G$5</xm:f>
+            <xm:f>Instruções!$A$3:$A$6</xm:f>
           </x14:formula1>
-          <xm:sqref>M3:M6457</xm:sqref>
+          <xm:sqref>E3:E1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E2412CD7-F840-4B18-9EE0-0EB2C86EBA0E}">
+          <x14:formula1>
+            <xm:f>Instruções!$C$3:$C$7</xm:f>
+          </x14:formula1>
+          <xm:sqref>F3:F1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{11DDE071-7C92-4D37-9379-4ADFD1483A76}">
           <x14:formula1>
             <xm:f>Instruções!$C$10:$C$11</xm:f>
           </x14:formula1>
-          <xm:sqref>P3:P6457</xm:sqref>
+          <xm:sqref>X3:X1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E5A8A6B5-9503-40D9-8734-778FC837BB6A}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6D0657BB-C840-4BB2-A2C7-C72D4E8C1860}">
           <x14:formula1>
-            <xm:f>Instruções!$I$3:$I$6</xm:f>
+            <xm:f>Instruções!$E$10:$E$17</xm:f>
           </x14:formula1>
-          <xm:sqref>Q3:Q6457</xm:sqref>
+          <xm:sqref>S3:S1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BD25C12D-0A9B-467C-A431-536F15A75328}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5F941123-C233-4C9E-9BF1-8D0385A99488}">
           <x14:formula1>
             <xm:f>Instruções!$G$10:$G$15</xm:f>
           </x14:formula1>
-          <xm:sqref>H3:H3595</xm:sqref>
+          <xm:sqref>P3:P1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
